--- a/output_data/charts/M100000US391416130899999.xlsx
+++ b/output_data/charts/M100000US391416130899999.xlsx
@@ -120,7 +120,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Population - Paxton Township (Ross) Township (unincorporated)</a:t>
+              <a:t>Population - Paxton Township (Ross)</a:t>
             </a:r>
           </a:p>
         </c:rich>
